--- a/.cloud_chaos_data/cloud_chaos_admin_export.xlsx
+++ b/.cloud_chaos_data/cloud_chaos_admin_export.xlsx
@@ -1,58 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="registrations" sheetId="1" r:id="rId1"/>
-    <sheet name="sessions" sheetId="2" r:id="rId2"/>
-    <sheet name="summary" sheetId="3" r:id="rId3"/>
-    <sheet name="pain_accuracy" sheetId="4" r:id="rId4"/>
+    <sheet name="registrations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="sessions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="pain_accuracy" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>total_players</t>
-  </si>
-  <si>
-    <t>total_sessions</t>
-  </si>
-  <si>
-    <t>perfect_count</t>
-  </si>
-  <si>
-    <t>avg_score</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +51,95 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -359,66 +427,565 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>last_seen</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>total_plays</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>best_score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>best_time</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>leaderboard_session_id</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>leaderboard_score</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>leaderboard_time_used</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>leaderboard_is_perfect</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>leaderboard_timed_out</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>leaderboard_completed_at</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>sync_status</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>last_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Live QA e5872847</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Live integration test</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>46277.39636587719</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>46277.39648808947</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>46277.39648712162</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>live_db</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Live QA 5a8bf0d2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Live integration test</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>46277.39712830652</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46277.39725610124</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>46277.39725511735</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>live_db</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Live QA 3f5d610c</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Live integration test</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46277.39479182259</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46277.39479182259</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>live_db</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>time_used</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>is_perfect</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>timed_out</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>completed_at</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>session_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Live QA e5872847</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Live integration test</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>46277.39648712162</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Live QA 5a8bf0d2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Live integration test</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>46277.39725511735</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>total_players</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>total_sessions</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>perfect_count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>avg_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>pain_idx</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>correct_count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>